--- a/backend/data/financials_by_company/1D5.SI.xlsx
+++ b/backend/data/financials_by_company/1D5.SI.xlsx
@@ -4010,10 +4010,8 @@
           <t>Johor Bahru</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>81200</t>
-        </is>
+      <c r="D2" t="n">
+        <v>81200</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4227,7 +4225,7 @@
         <v>-22290000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
@@ -4287,7 +4285,7 @@
         <v>0.108</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG2" t="n">
         <v>-0.02307</v>
@@ -4452,7 +4450,7 @@
         <v>1</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
         <v>-1.999992e-05</v>
